--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -442,13 +442,13 @@
         <v>本周套餐已更新</v>
       </c>
       <c r="C2" t="str">
-        <v>第30周套餐已发布，请查看可选品规和订购时间。</v>
+        <v>本周套餐已发布，请选择您的档位查看对应品规和数量。</v>
       </c>
       <c r="D2" t="str">
         <v>2026-07-30</v>
       </c>
       <c r="E2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="F2" t="str">
         <v>2026-07-30</v>
@@ -459,182 +459,656 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>本周四直播预告</v>
+        <v>应急订单安排已发布</v>
       </c>
       <c r="C3" t="str">
-        <v>本周四上午10:00，讲解最新分档政策和订货技巧。</v>
+        <v>本批次应急订单已发布，请查看截止时间并提前准备资金。</v>
       </c>
       <c r="D3" t="str">
         <v>2026-07-31</v>
       </c>
       <c r="E3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-07-30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>节假日配送调整通知</v>
-      </c>
-      <c r="C4" t="str">
-        <v>下周一因节假日调整，配送时间将顺延一天，请提前做好订货安排。</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-08-02</v>
-      </c>
-      <c r="E4" t="str">
-        <v>否</v>
-      </c>
-      <c r="F4" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I21"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>周次</v>
+        <v>品牌组</v>
       </c>
       <c r="B1" t="str">
-        <v>套餐名称</v>
+        <v>品牌</v>
       </c>
       <c r="C1" t="str">
-        <v>适用档位</v>
+        <v>品规名称</v>
       </c>
       <c r="D1" t="str">
-        <v>订购开始时间</v>
+        <v>30-28档数量</v>
       </c>
       <c r="E1" t="str">
-        <v>订购结束时间</v>
+        <v>27-20档数量</v>
       </c>
       <c r="F1" t="str">
-        <v>包含品规</v>
+        <v>19-15档数量</v>
       </c>
       <c r="G1" t="str">
-        <v>各品规数量</v>
+        <v>14-10档数量</v>
       </c>
       <c r="H1" t="str">
-        <v>注意事项</v>
+        <v>9-1档数量</v>
       </c>
       <c r="I1" t="str">
         <v>更新时间</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>30</v>
+      <c r="A2" t="str">
+        <v>上烟集团</v>
       </c>
       <c r="B2" t="str">
-        <v>标准套餐A</v>
+        <v>上烟集团</v>
       </c>
       <c r="C2" t="str">
-        <v>1-15档</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-07-31</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026-08-02</v>
-      </c>
-      <c r="F2" t="str">
-        <v>品牌A（硬盒）、品牌B（软盒）</v>
-      </c>
-      <c r="G2" t="str">
-        <v>品牌A: 5条, 品牌B: 3条</v>
-      </c>
-      <c r="H2" t="str">
-        <v>演示数据，不代表实际业务安排。请以正式通知为准。</v>
+        <v>中华(硬红)</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>30</v>
+      <c r="A3" t="str">
+        <v>上烟集团</v>
       </c>
       <c r="B3" t="str">
-        <v>标准套餐B</v>
+        <v>上烟集团</v>
       </c>
       <c r="C3" t="str">
-        <v>16-30档</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-08-04</v>
-      </c>
-      <c r="F3" t="str">
-        <v>品牌C（细支）、品牌D（中支）</v>
-      </c>
-      <c r="G3" t="str">
-        <v>品牌C: 4条, 品牌D: 2条</v>
-      </c>
-      <c r="H3" t="str">
-        <v>演示数据，不代表实际业务安排。请以正式通知为准。</v>
+        <v>沪前门(软)</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
       </c>
       <c r="I3" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>29</v>
+      <c r="A4" t="str">
+        <v>上烟集团</v>
       </c>
       <c r="B4" t="str">
-        <v>上期标准套餐</v>
+        <v>上烟集团</v>
       </c>
       <c r="C4" t="str">
-        <v>1-30档</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="F4" t="str">
-        <v>品牌A（硬盒）、品牌C（细支）</v>
-      </c>
-      <c r="G4" t="str">
-        <v>品牌A: 5条, 品牌C: 3条</v>
-      </c>
-      <c r="H4" t="str">
-        <v>演示数据。此套餐已结束。</v>
+        <v>牡丹(软)</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-07-25</v>
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>组1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C5" t="str">
+        <v>苏烟(软五星红杉树)</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>组1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C6" t="str">
+        <v>南京(硬炫赫门)</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>组2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C7" t="str">
+        <v>南京(硬大观园爆冰)</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>组2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C8" t="str">
+        <v>苏烟(硬五星红中)</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>组2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C9" t="str">
+        <v>南京(硬紫树)</v>
+      </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>组3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C10" t="str">
+        <v>南京(硬精品)</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>组3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C11" t="str">
+        <v>南京(硬十二钗薄荷)</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>组3</v>
+      </c>
+      <c r="B12" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C12" t="str">
+        <v>南京(硬红)</v>
+      </c>
+      <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>组4</v>
+      </c>
+      <c r="B13" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C13" t="str">
+        <v>南京(软九五)</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>组4</v>
+      </c>
+      <c r="B14" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C14" t="str">
+        <v>利群(硬新版)</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>组5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C15" t="str">
+        <v>南京(硬十二钗烤烟)</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>组5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>江苏中烟</v>
+      </c>
+      <c r="C16" t="str">
+        <v>黄山(硬新一品)</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>云南中烟</v>
+      </c>
+      <c r="B17" t="str">
+        <v>云南中烟</v>
+      </c>
+      <c r="C17" t="str">
+        <v>云烟(软珍品)</v>
+      </c>
+      <c r="D17">
+        <v>22</v>
+      </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>云南中烟</v>
+      </c>
+      <c r="B18" t="str">
+        <v>云南中烟</v>
+      </c>
+      <c r="C18" t="str">
+        <v>红塔山(软13mg经典1956)</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="B19" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="C19" t="str">
+        <v>七匹狼(硬银中支)</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="B20" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="C20" t="str">
+        <v>七匹狼(软灰)</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="B21" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="C21" t="str">
+        <v>七匹狼(纯境)</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-07-30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -644,10 +1118,10 @@
   <dimension ref="A1:G7"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
     <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
   </cols>
@@ -677,10 +1151,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>品牌A</v>
+        <v>中华</v>
       </c>
       <c r="B2" t="str">
-        <v>品牌A（硬盒）</v>
+        <v>中华(硬红)</v>
       </c>
       <c r="C2" t="str">
         <v>100.00</v>
@@ -700,10 +1174,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>品牌A</v>
+        <v>苏烟</v>
       </c>
       <c r="B3" t="str">
-        <v>品牌A（软盒）</v>
+        <v>苏烟(软五星红杉树)</v>
       </c>
       <c r="C3" t="str">
         <v>100.00</v>
@@ -723,10 +1197,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>品牌B</v>
+        <v>南京</v>
       </c>
       <c r="B4" t="str">
-        <v>品牌B（硬盒）</v>
+        <v>南京(硬炫赫门)</v>
       </c>
       <c r="C4" t="str">
         <v>100.00</v>
@@ -746,10 +1220,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>品牌B</v>
+        <v>南京</v>
       </c>
       <c r="B5" t="str">
-        <v>品牌B（细支）</v>
+        <v>南京(硬精品)</v>
       </c>
       <c r="C5" t="str">
         <v>100.00</v>
@@ -769,10 +1243,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>品牌C</v>
+        <v>云烟</v>
       </c>
       <c r="B6" t="str">
-        <v>品牌C（硬盒）</v>
+        <v>云烟(软珍品)</v>
       </c>
       <c r="C6" t="str">
         <v>100.00</v>
@@ -792,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>品牌D</v>
+        <v>七匹狼</v>
       </c>
       <c r="B7" t="str">
-        <v>品牌D（中支）</v>
+        <v>七匹狼(硬银中支)</v>
       </c>
       <c r="C7" t="str">
         <v>100.00</v>
@@ -822,186 +1296,80 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:D4"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>日期</v>
+        <v>批次</v>
       </c>
       <c r="B1" t="str">
-        <v>事项类型</v>
+        <v>订货日期</v>
       </c>
       <c r="C1" t="str">
-        <v>事项标题</v>
+        <v>送货日期</v>
       </c>
       <c r="D1" t="str">
-        <v>适用客户</v>
-      </c>
-      <c r="E1" t="str">
-        <v>具体安排</v>
-      </c>
-      <c r="F1" t="str">
-        <v>注意事项</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-30</v>
+        <v>第30周</v>
       </c>
       <c r="B2" t="str">
-        <v>正常订货</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C2" t="str">
-        <v>第30周正常订货日</v>
+        <v>2026-08-02</v>
       </c>
       <c r="D2" t="str">
-        <v>全部客户</v>
-      </c>
-      <c r="E2" t="str">
-        <v>请按时在订货系统中提交订单</v>
-      </c>
-      <c r="F2" t="str">
         <v>演示数据</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-31</v>
+        <v>第30周</v>
       </c>
       <c r="B3" t="str">
-        <v>直播</v>
+        <v>2026-08-01</v>
       </c>
       <c r="C3" t="str">
-        <v>每周四直播</v>
+        <v>2026-08-03</v>
       </c>
       <c r="D3" t="str">
-        <v>全部客户</v>
-      </c>
-      <c r="E3" t="str">
-        <v>上午10:00-11:00，直播链接请查看直播专区</v>
-      </c>
-      <c r="F3" t="str">
         <v>演示数据</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-08-01</v>
+        <v>第31周</v>
       </c>
       <c r="B4" t="str">
-        <v>扣款</v>
+        <v>2026-08-07</v>
       </c>
       <c r="C4" t="str">
-        <v>银行扣款日</v>
+        <v>2026-08-09</v>
       </c>
       <c r="D4" t="str">
-        <v>签约代扣客户</v>
-      </c>
-      <c r="E4" t="str">
-        <v>请确保账户余额充足</v>
-      </c>
-      <c r="F4" t="str">
-        <v>演示数据，请以银行通知为准</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-08-02</v>
-      </c>
-      <c r="B5" t="str">
-        <v>配送</v>
-      </c>
-      <c r="C5" t="str">
-        <v>配送日</v>
-      </c>
-      <c r="D5" t="str">
-        <v>城区客户</v>
-      </c>
-      <c r="E5" t="str">
-        <v>当天送达，请保持电话畅通</v>
-      </c>
-      <c r="F5" t="str">
         <v>演示数据</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-08-03</v>
-      </c>
-      <c r="B6" t="str">
-        <v>配送</v>
-      </c>
-      <c r="C6" t="str">
-        <v>配送日</v>
-      </c>
-      <c r="D6" t="str">
-        <v>乡镇客户</v>
-      </c>
-      <c r="E6" t="str">
-        <v>当天送达，请保持电话畅通</v>
-      </c>
-      <c r="F6" t="str">
-        <v>演示数据</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026-08-04</v>
-      </c>
-      <c r="B7" t="str">
-        <v>应急订单</v>
-      </c>
-      <c r="C7" t="str">
-        <v>应急订单处理</v>
-      </c>
-      <c r="D7" t="str">
-        <v>部分客户</v>
-      </c>
-      <c r="E7" t="str">
-        <v>具体安排详见应急订单页面</v>
-      </c>
-      <c r="F7" t="str">
-        <v>演示数据</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2026-08-09</v>
-      </c>
-      <c r="B8" t="str">
-        <v>节假日调整</v>
-      </c>
-      <c r="C8" t="str">
-        <v>节假日订货时间调整</v>
-      </c>
-      <c r="D8" t="str">
-        <v>全部客户</v>
-      </c>
-      <c r="E8" t="str">
-        <v>因节假日，订货时间提前至上午截止</v>
-      </c>
-      <c r="F8" t="str">
-        <v>演示数据，以正式通知为准</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1051,7 +1419,7 @@
         <v>最新分档政策解读</v>
       </c>
       <c r="C2" t="str">
-        <v>详细介绍最新档位评定标准和规则变化，帮助客户了解分档政策</v>
+        <v>详细介绍最新档位评定标准和规则变化</v>
       </c>
       <c r="D2" t="str">
         <v>王经理</v>
@@ -1072,74 +1440,16 @@
         <v>2026-07-30</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-07-23 10:00</v>
-      </c>
-      <c r="B3" t="str">
-        <v>订货系统操作培训</v>
-      </c>
-      <c r="C3" t="str">
-        <v>手把手教学订货系统操作流程</v>
-      </c>
-      <c r="D3" t="str">
-        <v>李经理</v>
-      </c>
-      <c r="E3" t="str">
-        <v>https://example.com/live/demo2</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>https://example.com/replay/demo2</v>
-      </c>
-      <c r="H3" t="str">
-        <v>可回看</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-07-23</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-07-16 10:00</v>
-      </c>
-      <c r="B4" t="str">
-        <v>新品品鉴会</v>
-      </c>
-      <c r="C4" t="str">
-        <v>近期新品介绍和品鉴</v>
-      </c>
-      <c r="D4" t="str">
-        <v>张经理</v>
-      </c>
-      <c r="E4" t="str">
-        <v>https://example.com/live/demo3</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>已结束</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-07-16</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1180,10 +1490,10 @@
         <v>客户档位是烟草公司根据客户经营情况评定的等级，不同档位对应不同的订货权限。</v>
       </c>
       <c r="D2" t="str">
-        <v>卷烟零售客户档位制度是根据客户的经营能力、规范程度和历史数据，将客户分为不同等级的管理制度。档位越高，通常意味着可以订购的品规种类和数量越多。档位评定周期一般为每月或每季度进行一次动态调整。客户档位是合理安排货源投放的重要依据。</v>
+        <v>卷烟零售客户档位制度是根据客户的经营能力、规范程度和历史数据，将客户分为不同等级的管理制度。档位越高，通常意味着可以订购的品规种类和数量越多。</v>
       </c>
       <c r="E2" t="str">
-        <v>[{"q":"档位多久调整一次？","a":"演示数据，具体调整周期以当地烟草公司正式通知为准，一般为月度或季度调整。"},{"q":"档位评定结果如何查询？","a":"档位评定结果可在订货系统中查询，也可咨询您的客户经理。演示数据，具体以正式系统为准。"}]</v>
+        <v>[{"q":"档位多久调整一次？","a":"演示数据，具体调整周期以当地烟草公司正式通知为准。"}]</v>
       </c>
       <c r="F2" t="str">
         <v>2026-07-30</v>
@@ -1197,58 +1507,32 @@
         <v>档位评定的主要依据</v>
       </c>
       <c r="C3" t="str">
-        <v>评定依据主要包括客户的订货量、订货金额、规范经营情况和配合度等多个维度。</v>
+        <v>评定依据主要包括客户的订货量、订货金额、规范经营情况等多个维度。</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
         <v xml:space="preserve">档位评定的主要维度包括：
-1. 订货量维度：客户的月均订货量在辖区内排名情况。
-2. 订货金额维度：客户的月均订货金额排名情况。
-3. 规范经营维度：客户是否存在违规记录。
-4. 配合度维度：客户在信息采集、品牌培育等方面的配合情况。
-各维度按一定权重计算综合得分，按得分排名确定档位。</v>
+1. 订货量维度
+2. 订货金额维度
+3. 规范经营维度
+4. 配合度维度</v>
       </c>
       <c r="E3" t="str">
-        <v>[{"q":"评定分数如何计算？","a":"演示数据，具体评分标准和权重以当地烟草公司正式发布的评定办法为准。"},{"q":"如何提升档位？","a":"建议保持稳定订货，积极配合各项工作，具体提升策略可咨询客户经理。演示数据仅供参考。"}]</v>
+        <v>[{"q":"如何提升档位？","a":"建议保持稳定订货，积极配合各项工作，具体可咨询客户经理。演示数据仅供参考。"}]</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-07-30</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>注意事项</v>
-      </c>
-      <c r="B4" t="str">
-        <v>档位管理注意事项</v>
-      </c>
-      <c r="C4" t="str">
-        <v>了解档位管理中的重要规则和常见问题，避免因不了解规则影响经营。</v>
-      </c>
-      <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">档位管理中需要注意以下几点：
-1. 档位评定数据以烟草公司系统记录为准。
-2. 连续多期未订货可能会影响档位评定。
-3. 存在违规经营记录将影响档位评定结果。
-4. 档位调整后，订货权限将按新档位执行。
-5. 对档位评定有疑问，请及时联系客户经理。</v>
-      </c>
-      <c r="E4" t="str">
-        <v>[{"q":"档位被降低怎么办？","a":"请联系您的客户经理了解具体原因，并根据建议进行改进。演示数据，以正式通知为准。"},{"q":"新入网客户的初始档位？","a":"新入网客户一般设置初始档位，具体档位请咨询客户经理。演示数据。"}]</v>
-      </c>
-      <c r="F4" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1292,25 +1576,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7月应急订单安排（第一批）</v>
+        <v>应急订单安排（演示）</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-31</v>
       </c>
       <c r="C2" t="str">
         <v>2026年7月第一批</v>
       </c>
       <c r="D2" t="str">
-        <v>品牌A（硬盒）、品牌B（细支）</v>
+        <v>中华(硬红)、苏烟(软五星红杉树)</v>
       </c>
       <c r="E2" t="str">
-        <v>1-15档客户</v>
+        <v>全部客户</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-03</v>
+        <v>2026-08-02</v>
       </c>
       <c r="G2" t="str">
-        <v>演示数据。工业到货后及时安排兑付，请提前确认账户资金充足。具体到货时间以实际为准，不做不准确承诺。</v>
+        <v>演示数据。工业到货后及时安排兑付，请提前确认账户资金充足。</v>
       </c>
       <c r="H2" t="str">
         <v>进行中</v>
@@ -1319,45 +1603,16 @@
         <v>2026-07-30</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>6月应急订单安排（第三批）</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-07-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026年6月第三批</v>
-      </c>
-      <c r="D3" t="str">
-        <v>品牌C（中支）</v>
-      </c>
-      <c r="E3" t="str">
-        <v>16-30档客户</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-07-29</v>
-      </c>
-      <c r="G3" t="str">
-        <v>演示数据。此批次已结束。</v>
-      </c>
-      <c r="H3" t="str">
-        <v>已结束</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-07-26</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -1389,47 +1644,23 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>客户经理姓名</v>
+        <v>数据更新时间</v>
       </c>
       <c r="B4" t="str">
-        <v>王经理</v>
+        <v>2026-07-30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>客户经理联系电话</v>
+        <v>页脚说明</v>
       </c>
       <c r="B5" t="str">
-        <v>0512-12345678</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>数据更新时间</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-07-30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>页脚说明</v>
-      </c>
-      <c r="B7" t="str">
         <v>本页面仅面向持证卷烟零售客户提供业务信息查询和服务提醒</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>是否显示联系方式</v>
-      </c>
-      <c r="B8" t="str">
-        <v>是</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -483,12 +483,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
@@ -505,24 +505,27 @@
         <v>品牌</v>
       </c>
       <c r="C1" t="str">
+        <v>类型</v>
+      </c>
+      <c r="D1" t="str">
         <v>品规名称</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>30-28档数量</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>27-20档数量</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>19-15档数量</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>14-10档数量</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>9-1档数量</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>更新时间</v>
       </c>
     </row>
@@ -534,24 +537,27 @@
         <v>上烟集团</v>
       </c>
       <c r="C2" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D2" t="str">
         <v>中华(硬红)</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>25</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>8</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -563,24 +569,27 @@
         <v>上烟集团</v>
       </c>
       <c r="C3" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D3" t="str">
         <v>沪前门(软)</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>25</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>20</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -592,24 +601,27 @@
         <v>上烟集团</v>
       </c>
       <c r="C4" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D4" t="str">
         <v>牡丹(软)</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>15</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -621,24 +633,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C5" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D5" t="str">
         <v>苏烟(软五星红杉树)</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>24</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>16</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -650,24 +665,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C6" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D6" t="str">
         <v>南京(硬炫赫门)</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>16</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>12</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>7</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -679,24 +697,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C7" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D7" t="str">
         <v>南京(硬大观园爆冰)</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>15</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v/>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -708,24 +729,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C8" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D8" t="str">
         <v>苏烟(硬五星红中)</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v/>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -737,24 +761,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C9" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D9" t="str">
         <v>南京(硬紫树)</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>18</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>13</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>7</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v/>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -766,24 +793,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C10" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D10" t="str">
         <v>南京(硬精品)</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>10</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>3</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>2</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -795,24 +825,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C11" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D11" t="str">
         <v>南京(硬十二钗薄荷)</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>8</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>2</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -824,24 +857,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C12" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D12" t="str">
         <v>南京(硬红)</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>15</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>12</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>7</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>4</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>2</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -853,24 +889,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C13" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D13" t="str">
         <v>南京(软九五)</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>4</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -882,24 +921,27 @@
         <v>江苏中烟</v>
       </c>
       <c r="C14" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D14" t="str">
         <v>利群(硬新版)</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
         <v>1</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -911,16 +953,16 @@
         <v>江苏中烟</v>
       </c>
       <c r="C15" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D15" t="str">
         <v>南京(硬十二钗烤烟)</v>
-      </c>
-      <c r="D15">
-        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -928,7 +970,10 @@
       <c r="H15">
         <v>4</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -940,16 +985,16 @@
         <v>江苏中烟</v>
       </c>
       <c r="C16" t="str">
+        <v>活动品规</v>
+      </c>
+      <c r="D16" t="str">
         <v>黄山(硬新一品)</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
       </c>
       <c r="E16">
         <v>9</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -957,7 +1002,10 @@
       <c r="H16">
         <v>6</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -969,24 +1017,27 @@
         <v>云南中烟</v>
       </c>
       <c r="C17" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D17" t="str">
         <v>云烟(软珍品)</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>22</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>18</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>12</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>7</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>4</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -998,24 +1049,27 @@
         <v>云南中烟</v>
       </c>
       <c r="C18" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D18" t="str">
         <v>红塔山(软13mg经典1956)</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>25</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>20</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>15</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>8</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>5</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -1027,24 +1081,27 @@
         <v>福建中烟</v>
       </c>
       <c r="C19" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D19" t="str">
         <v>七匹狼(硬银中支)</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>5</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>3</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>2</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -1056,24 +1113,27 @@
         <v>福建中烟</v>
       </c>
       <c r="C20" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D20" t="str">
         <v>七匹狼(软灰)</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>3</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
-      <c r="G20" t="str">
-        <v/>
+      <c r="G20">
+        <v>2</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
@@ -1085,30 +1145,33 @@
         <v>福建中烟</v>
       </c>
       <c r="C21" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D21" t="str">
         <v>七匹狼(纯境)</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>6</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>4</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>3</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>2026-07-30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J21"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -1359,12 +1359,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C23"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1377,55 +1376,252 @@
       <c r="C1" t="str">
         <v>送货日期</v>
       </c>
-      <c r="D1" t="str">
-        <v>备注</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>第30周</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-02</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-02</v>
-      </c>
-      <c r="D2" t="str">
-        <v>演示数据</v>
+        <v>2026-08-04</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>第30周</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-08-01</v>
+        <v>2026-08-03</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-03</v>
-      </c>
-      <c r="D3" t="str">
-        <v>演示数据</v>
+        <v>2026-08-05</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>第31周</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v>2026-08-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-08-06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="C5" t="str">
         <v>2026-08-07</v>
       </c>
-      <c r="C4" t="str">
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-08-08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
         <v>2026-08-09</v>
       </c>
-      <c r="D4" t="str">
-        <v>演示数据</v>
+      <c r="C7" t="str">
+        <v>2026-08-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-08-12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-08-13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-08-15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-08-16</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-08-18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-08-19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-08-20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-08-21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-08-22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-08-25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-08-26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-08-25</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-08-27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-08-26</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-08-28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-08-29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-09-02</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -483,7 +483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
@@ -537,7 +537,7 @@
         <v>上烟集团</v>
       </c>
       <c r="C2" t="str">
-        <v>激励品规</v>
+        <v>活动品规</v>
       </c>
       <c r="D2" t="str">
         <v>中华(硬红)</v>
@@ -665,7 +665,7 @@
         <v>江苏中烟</v>
       </c>
       <c r="C6" t="str">
-        <v>活动品规</v>
+        <v>激励品规</v>
       </c>
       <c r="D6" t="str">
         <v>南京(硬炫赫门)</v>
@@ -761,7 +761,7 @@
         <v>江苏中烟</v>
       </c>
       <c r="C9" t="str">
-        <v>活动品规</v>
+        <v>激励品规</v>
       </c>
       <c r="D9" t="str">
         <v>南京(硬紫树)</v>
@@ -857,7 +857,7 @@
         <v>江苏中烟</v>
       </c>
       <c r="C12" t="str">
-        <v>活动品规</v>
+        <v>激励品规</v>
       </c>
       <c r="D12" t="str">
         <v>南京(硬红)</v>
@@ -921,19 +921,19 @@
         <v>江苏中烟</v>
       </c>
       <c r="C14" t="str">
-        <v>活动品规</v>
+        <v>激励品规</v>
       </c>
       <c r="D14" t="str">
-        <v>利群(硬新版)</v>
+        <v>南京(硬紫树)</v>
       </c>
       <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
         <v>2</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -947,31 +947,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>组5</v>
+        <v>组4</v>
       </c>
       <c r="B15" t="str">
         <v>江苏中烟</v>
       </c>
       <c r="C15" t="str">
-        <v>活动品规</v>
+        <v>激励品规</v>
       </c>
       <c r="D15" t="str">
-        <v>南京(硬十二钗烤烟)</v>
+        <v>利群(硬新版)</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>4</v>
-      </c>
-      <c r="H15">
-        <v>4</v>
-      </c>
-      <c r="I15">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
       <c r="J15" t="str">
         <v>2026-07-30</v>
@@ -988,22 +988,22 @@
         <v>活动品规</v>
       </c>
       <c r="D16" t="str">
-        <v>黄山(硬新一品)</v>
+        <v>南京(硬十二钗烤烟)</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J16" t="str">
         <v>2026-07-30</v>
@@ -1011,31 +1011,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>云南中烟</v>
+        <v>组5</v>
       </c>
       <c r="B17" t="str">
-        <v>云南中烟</v>
+        <v>江苏中烟</v>
       </c>
       <c r="C17" t="str">
         <v>激励品规</v>
       </c>
       <c r="D17" t="str">
-        <v>云烟(软珍品)</v>
+        <v>黄山(硬新一品)</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17" t="str">
         <v>2026-07-30</v>
@@ -1049,25 +1049,25 @@
         <v>云南中烟</v>
       </c>
       <c r="C18" t="str">
-        <v>激励品规</v>
+        <v>活动品规</v>
       </c>
       <c r="D18" t="str">
-        <v>红塔山(软13mg经典1956)</v>
+        <v>云烟(软珍品)</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="str">
         <v>2026-07-30</v>
@@ -1075,31 +1075,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>福建中烟</v>
+        <v>云南中烟</v>
       </c>
       <c r="B19" t="str">
-        <v>福建中烟</v>
+        <v>云南中烟</v>
       </c>
       <c r="C19" t="str">
         <v>激励品规</v>
       </c>
       <c r="D19" t="str">
-        <v>七匹狼(硬银中支)</v>
+        <v>红塔山(软13mg经典1956)</v>
       </c>
       <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+      <c r="I19">
         <v>5</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
       </c>
       <c r="J19" t="str">
         <v>2026-07-30</v>
@@ -1113,16 +1113,16 @@
         <v>福建中烟</v>
       </c>
       <c r="C20" t="str">
-        <v>激励品规</v>
+        <v>活动品规</v>
       </c>
       <c r="D20" t="str">
-        <v>七匹狼(软灰)</v>
+        <v>七匹狼(硬银中支)</v>
       </c>
       <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
         <v>3</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1145,19 +1145,19 @@
         <v>福建中烟</v>
       </c>
       <c r="C21" t="str">
-        <v>激励品规</v>
+        <v>活动品规</v>
       </c>
       <c r="D21" t="str">
-        <v>七匹狼(纯境)</v>
+        <v>七匹狼(软灰)</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1169,9 +1169,41 @@
         <v>2026-07-30</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="B22" t="str">
+        <v>福建中烟</v>
+      </c>
+      <c r="C22" t="str">
+        <v>激励品规</v>
+      </c>
+      <c r="D22" t="str">
+        <v>七匹狼(纯境)</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>2026-07-30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="13020"/>
+    <workbookView windowWidth="29400" windowHeight="13000"/>
   </bookViews>
   <sheets>
     <sheet name="首页通知" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="147">
   <si>
     <t>排序</t>
   </si>
@@ -66,10 +66,10 @@
     <t>否</t>
   </si>
   <si>
-    <t>应急订单安排已发布</t>
-  </si>
-  <si>
-    <t>本批次应急订单已发布，请查看截止时间并提前准备资金。</t>
+    <t>8月订货安排已发布</t>
+  </si>
+  <si>
+    <t>请选择好自己的批次后查看</t>
   </si>
   <si>
     <t>2026-07-31</t>
@@ -452,24 +452,6 @@
   </si>
   <si>
     <t>当前状态</t>
-  </si>
-  <si>
-    <t>应急订单安排（演示）</t>
-  </si>
-  <si>
-    <t>2026年7月第一批</t>
-  </si>
-  <si>
-    <t>中华(硬红)、苏烟(软五星红杉树)</t>
-  </si>
-  <si>
-    <t>全部客户</t>
-  </si>
-  <si>
-    <t>演示数据。工业到货后及时安排兑付，请提前确认账户资金充足。</t>
-  </si>
-  <si>
-    <t>进行中</t>
   </si>
   <si>
     <t>键名</t>
@@ -1577,7 +1559,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A2 D2:F2 A3:F3" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:A3 D2:F3 A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2934,8 +2916,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="1"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="30.8303571428571" customWidth="1"/>
     <col min="2" max="2" width="14.8303571428571" customWidth="1"/>
@@ -2975,40 +2957,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3025,31 +2978,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -3057,10 +3010,10 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="13000" activeTab="6"/>
+    <workbookView windowWidth="29400" windowHeight="13000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="首页通知" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="157">
   <si>
     <t>排序</t>
   </si>
@@ -54,30 +54,36 @@
     <t>更新时间</t>
   </si>
   <si>
-    <t>本周套餐已更新</t>
-  </si>
-  <si>
-    <t>本周套餐已发布，请选择您的档位查看对应品规和数量。</t>
+    <t>7.26-7.30标签活动已更新</t>
+  </si>
+  <si>
+    <t>标签活动已发布，请选择您的档位查看对应品规和数量。</t>
   </si>
   <si>
     <t>2026-07-31</t>
   </si>
   <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>应急订单安排已发布</t>
+  </si>
+  <si>
+    <t>本批次应急订单已发布，请查看截止时间并提前准备资金。</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>周四直播</t>
+  </si>
+  <si>
+    <t>企业微信每周四下午3点的疯狂星期四直播欢迎观看！</t>
+  </si>
+  <si>
     <t>否</t>
   </si>
   <si>
-    <t>应急订单安排已发布</t>
-  </si>
-  <si>
-    <t>本批次应急订单已发布，请查看截止时间并提前准备资金。</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>品牌组</t>
   </si>
   <si>
@@ -420,14 +426,13 @@
     <t>档位评定的主要依据</t>
   </si>
   <si>
-    <t>评定依据主要包括客户的订货量、订货金额、规范经营情况等多个维度。</t>
+    <t>评定依据主要包括客户的订货量、订货金额、信用等级等多个维度。</t>
   </si>
   <si>
     <t>档位评定的主要维度包括：
 1. 订货量维度
 2. 订货金额维度
-3. 规范经营维度
-4. 配合度维度</t>
+3.信用等级</t>
   </si>
   <si>
     <t>[{"q":"如何提升档位？","a":"建议保持稳定订货，积极配合各项工作，具体可咨询客户经理。演示数据仅供参考。"}]</t>
@@ -454,19 +459,19 @@
     <t>当前状态</t>
   </si>
   <si>
-    <t>应急订单安排（演示）</t>
-  </si>
-  <si>
-    <t>2026年7月第一批</t>
-  </si>
-  <si>
-    <t>中华(硬红)、苏烟(软五星红杉树)</t>
-  </si>
-  <si>
-    <t>全部客户</t>
-  </si>
-  <si>
-    <t>演示数据。工业到货后及时安排兑付，请提前确认账户资金充足。</t>
+    <t>应急订单安排</t>
+  </si>
+  <si>
+    <t>2026年6月21日-6.25日</t>
+  </si>
+  <si>
+    <t>南京（硬红）</t>
+  </si>
+  <si>
+    <t>参加相关活动的客户下午4点前</t>
+  </si>
+  <si>
+    <t>工业到货后及时安排兑付，请提前确认账户资金充足。</t>
   </si>
   <si>
     <t>进行中</t>
@@ -1123,8 +1128,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1508,8 +1516,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.83035714285714" customWidth="1"/>
     <col min="2" max="2" width="25.8303571428571" customWidth="1"/>
@@ -1573,9 +1581,29 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1583,7 +1611,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A2 D2 F2 A3:F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1603,31 +1631,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -1635,16 +1663,16 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>25</v>
@@ -1667,16 +1695,16 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>25</v>
@@ -1699,16 +1727,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>15</v>
@@ -1731,16 +1759,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>24</v>
@@ -1763,16 +1791,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -1795,16 +1823,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1819,7 +1847,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
         <v>8</v>
@@ -1827,16 +1855,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1851,7 +1879,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J8" t="s">
         <v>8</v>
@@ -1859,16 +1887,16 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>18</v>
@@ -1883,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
         <v>8</v>
@@ -1891,16 +1919,16 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1923,16 +1951,16 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1955,16 +1983,16 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>15</v>
@@ -1987,16 +2015,16 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -2008,10 +2036,10 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
         <v>8</v>
@@ -2019,16 +2047,16 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -2040,10 +2068,10 @@
         <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J14" t="s">
         <v>8</v>
@@ -2051,16 +2079,16 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2072,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J15" t="s">
         <v>8</v>
@@ -2083,16 +2111,16 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2115,16 +2143,16 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -2147,16 +2175,16 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>22</v>
@@ -2179,16 +2207,16 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>25</v>
@@ -2211,16 +2239,16 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -2232,10 +2260,10 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
         <v>8</v>
@@ -2243,16 +2271,16 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2264,10 +2292,10 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
         <v>8</v>
@@ -2275,16 +2303,16 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2296,10 +2324,10 @@
         <v>3</v>
       </c>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
         <v>8</v>
@@ -2331,22 +2359,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -2354,22 +2382,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -2377,22 +2405,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -2400,22 +2428,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
         <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -2423,22 +2451,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
         <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
@@ -2446,22 +2474,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -2469,22 +2497,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -2511,13 +2539,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2525,10 +2553,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2536,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2547,10 +2575,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2558,10 +2586,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2569,10 +2597,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2580,10 +2608,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2591,10 +2619,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2602,10 +2630,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2613,10 +2641,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2624,10 +2652,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2635,10 +2663,10 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2646,10 +2674,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2657,10 +2685,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2668,10 +2696,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2679,10 +2707,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2690,10 +2718,10 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2701,10 +2729,10 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2712,10 +2740,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2723,10 +2751,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2734,10 +2762,10 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2745,10 +2773,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2756,10 +2784,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2789,28 +2817,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -2818,28 +2846,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -2870,19 +2898,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -2890,39 +2918,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="71" spans="1:6">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -2932,7 +2960,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F2 A3:B3 E3:F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2957,25 +2985,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -2983,28 +3011,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -3014,7 +3042,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 B2 F2 H2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3031,31 +3059,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -3063,18 +3091,18 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -404,15 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,16 +431,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>本周套餐已更新</v>
+        <v>7.26-7.30标签活动已更新</v>
       </c>
       <c r="C2" t="str">
-        <v>本周套餐已发布，请选择您的档位查看对应品规和数量。</v>
+        <v>标签活动已发布，请选择您的档位查看对应品规和数量。</v>
       </c>
       <c r="D2" t="str">
         <v>2026-07-31</v>
       </c>
       <c r="E2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="F2" t="str">
         <v>2026-07-31</v>
@@ -474,9 +466,30 @@
         <v>2026-07-31</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>周四直播</v>
+      </c>
+      <c r="C4" t="str">
+        <v>企业微信每周四下午3点的疯狂星期四直播欢迎观看！</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v>否</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-07-31</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -484,20 +497,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L32"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1425,15 +1424,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1597,6 +1587,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
@@ -1606,11 +1597,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1866,6 +1852,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
@@ -1875,17 +1862,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1946,6 +1922,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
@@ -1955,14 +1932,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="50.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2012,14 +1981,13 @@
         <v>档位评定的主要依据</v>
       </c>
       <c r="C3" t="str">
-        <v>评定依据主要包括客户的订货量、订货金额、规范经营情况等多个维度。</v>
+        <v>评定依据主要包括客户的订货量、订货金额、信用等级等多个维度。</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
         <v xml:space="preserve">档位评定的主要维度包括：
 1. 订货量维度
 2. 订货金额维度
-3. 规范经营维度
-4. 配合度维度</v>
+3.信用等级</v>
       </c>
       <c r="E3" t="str">
         <v>[{"q":"如何提升档位？","a":"建议保持稳定订货，积极配合各项工作，具体可咨询客户经理。演示数据仅供参考。"}]</v>
@@ -2029,6 +1997,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
@@ -2038,17 +2007,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2081,25 +2039,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>应急订单安排（演示）</v>
+        <v>应急订单安排</v>
       </c>
       <c r="B2" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="C2" t="str">
-        <v>2026年7月第一批</v>
+        <v>2026年6月21日-6.25日</v>
       </c>
       <c r="D2" t="str">
-        <v>中华(硬红)、苏烟(软五星红杉树)</v>
+        <v>南京（硬红）</v>
       </c>
       <c r="E2" t="str">
-        <v>全部客户</v>
+        <v>参加相关活动的客户下午4点前</v>
       </c>
       <c r="F2" t="str">
         <v>2026-08-03</v>
       </c>
       <c r="G2" t="str">
-        <v>演示数据。工业到货后及时安排兑付，请提前确认账户资金充足。</v>
+        <v>工业到货后及时安排兑付，请提前确认账户资金充足。</v>
       </c>
       <c r="H2" t="str">
         <v>进行中</v>
@@ -2109,6 +2067,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
@@ -2118,10 +2077,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
